--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Job.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Job.xlsx
@@ -505,7 +505,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Guerreiro</t>
+          <t>guerreiro</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -520,7 +520,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Guerreiros usam seus corpos como armas, destruindo implacavelmente os obstáculos em seu caminho. Embora possam não ser habilidosos com magia, sua impressionante destreza em combate é inegável.</t>
+          <t>Guerreiros usam o próprio corpo como arma, destruindo sem piedade os obstáculos no caminho. Podem não ser hábeis com magia, mas seu poder de combate impressionante é inegável.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -547,7 +547,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ladrão</t>
+          <t>ladrão</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ladrões ganham a vida extraindo itens valiosos de tumbas e ruínas, movidos pela atração do tesouro. Possuem boas habilidades em combate e uma habilidade especial para negociar com mercadores.</t>
+          <t>Ladrões ganham a vida extraindo itens valiosos de tumbas e ruínas, atraídos pelo canto do tesouro. Têm perícia de combate decente e faro para negociar com mercadores.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -589,7 +589,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mago</t>
+          <t>mago</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Como o nome sugere, magos são especialistas na arte da magia. Sua sobrevivência depende de obter e gerenciar seus grimórios.</t>
+          <t>Como o nome sugere, magos dominam a arte da magia. Sua sobrevivência depende de conseguir e administrar seus livros de feitiços.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fazendeiro</t>
+          <t>fazendeiro</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fazendeiros são profissionais que se destacam na produção. São resilientes e possuem uma boa quantidade de habilidades físicas.</t>
+          <t>Fazendeiros são profissionais que se destacam na produção. São resilientes e possuem boa capacidade física.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Arqueiro</t>
+          <t>arqueiro</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Arqueiros são especialistas em ataques à distância. Podem ter algumas habilidades em combate corpo a corpo, mas geralmente derrotam inimigos à distância, sem permitir que se aproximem.</t>
+          <t>Arqueiros são especialistas em ataques à distância. Podem ter alguma capacidade corpo a corpo, mas normalmente derrotam inimigos de longe, sem deixá-los chegar perto.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mago de Batalha</t>
+          <t>mago de guerra</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mago de batalha é uma classe intermediária entre guerreiros e magos, com foco no combate corpo a corpo. Para dominar a magia, eles devem encontrar um equilíbrio e evoluir em ambas as áreas.</t>
+          <t>Magos de guerra representam uma classe intermediária entre guerreiros e magos, com foco no combate corpo a corpo. Para dominar a magia, precisam crescer em equilíbrio nas duas áreas.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turista</t>
+          <t>turista</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Turistas são uma classe tradicional neste mundo, e são previsivelmente frágeis.</t>
+          <t>Turistas são uma classe tradicional deste mundo e, previsivelmente, frágeis.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pianista</t>
+          <t>pianista</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pianistas, os profissionais solitários, ganham a vida através de suas apresentações. Sempre sobrecarregados com seus pianos, possuem uma capacidade notável de suportar cargas pesadas.</t>
+          <t>Pianistas, os profissionais solitários, vivem de suas apresentações. Sempre sob o fardo de seus pianos, têm uma capacidade notável de carregar peso.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sacerdote</t>
+          <t>sacerdote</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Junto com suas habilidades mágicas, sacerdotes possuem certa aptidão para combate corpo a corpo. Sua fé inabalável permite que recebam as máximas bênçãos dos deuses que servem.</t>
+          <t>Além das habilidades mágicas, sacerdotes possuem certa aptidão para o combate corpo a corpo. Sua fé inabalável lhes permite receber as bênçãos máximas dos deuses que servem.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atirador</t>
+          <t>atirador</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Atiradores são especialistas em armamentos modernos, habilidosos no manuseio de armas de fogo e explosivos. São capazes de operar habilmente as mais recentes armas produzidas por Yerl, assim como artefatos de antigas máquinas.</t>
+          <t>Atiradores são especialistas em armamento moderno, hábeis com armas de fogo e explosivos. Operam com destreza as armas mais recentes produzidas por Yerl, além de artefatos da maquinaria ancestral.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Inquisidor</t>
+          <t>inquisidor</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Inquisidores são clérigos apaixonados por erradicar heresias e outras crenças. São habilidosos no uso de armas de fogo e se destacam em manobras ágeis com equipamentos leves. Inquisidores podem excomungar adversários, privando-os da graça divina.</t>
+          <t>Inquisidores são clérigos apaixonados por erradicar a heresia e as outras fés. São hábeis com armas de fogo e excelentes em manobras ágeis com equipamento leve. Inquisidores podem excomungar adversários, tirando deles a graça divina.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Paladino</t>
+          <t>paladino</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Paladinos são guerreiros zelosos que juram lealdade a sua divindade. Empunham armas de duas mãos e estão sempre na linha de frente da batalha, protegendo seus aliados. Os paladinos de Jure são particularmente renomados por sua devoção e bravura.</t>
+          <t>Paladinos são guerreiros zelosos que juram lealdade à sua divindade. Empunham armas de duas mãos e estão sempre na frente de batalha, protegendo seus aliados. Os paladinos de Jure são particularmente renomados pela devoção e bravura.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bruxa</t>
+          <t>bruxa</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bruxas manipulam os segredos da alquimia e ganham a vida criando poções misteriosas. Também são ricas em conhecimento mágico, tornando-as adversárias problemáticas com sua tendência a lançar venenos, lançar maldições e usar artefatos mágicos. Levam vidas despreocupadas com seus gatos pretos, vendendo poções para os moradores das cidades e viajando pelo mundo em suas vassouras.</t>
+          <t>Bruxas manipulam os segredos da alquimia e vivem preparando poções misteriosas. Ricas em conhecimento mágico, são adversárias bem chatas de enfrentar, com sua mania de arremessar venenos, lançar maldições e usar artefatos mágicos. Levam vidas despreocupadas com seus gatos negros, vendendo poções ao povão e viajando o mundo em suas vassouras.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Executor</t>
+          <t>algoz</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Os executores são especialistas hereditários na execução, nomeados pelo rei através das gerações. São experientes no manuseio de armas, do corpo humano e no conhecimento de esferas de ferro para realizar execuções com eficiência. Abraçam a morte e podem liberar todo o seu poder quando estão à beira da morte.</t>
+          <t>Os algozes são especialistas hereditários na execução, nomeados pelo rei através de gerações. Conhecem armas, o corpo humano e a ciência das bolas de ferro para realizar execuções com fluidez. Acolhem a morte e conseguem liberar todo o poder quando estão à beira dela.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sábio da Espada</t>
+          <t>santo da espada</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sábios da espada são praticantes espirituais que transitam entre o mundo dos espíritos e o reino mortal, com o poder de repelir espíritos malignos. Habilidosos nas artes de maldições e adivinhação, dominam a técnica de aprimorar armas com talismãs infundidos com feitiçarias.</t>
+          <t>Santos da espada são praticantes espirituais que transitam entre o mundo dos espíritos e o dos mortais, com o poder de repelir espíritos malignos. Hábeis nas artes das maldições e da adivinhação, dominam a técnica de aprimorar armas com talismãs imbuídos de feitiços.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Predador</t>
+          <t>predador</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bardo</t>
+          <t>bardo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alquimista</t>
+          <t>alquimista</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Defensor</t>
+          <t>defensor</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nenhum</t>
+          <t>nenhum</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
